--- a/Ethanol_Water_Steady_State_Separation_Recycle_Model/Ethanol_Water_Material_Balance_Model.xlsx
+++ b/Ethanol_Water_Steady_State_Separation_Recycle_Model/Ethanol_Water_Material_Balance_Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3AF6BDB6FD02CC28/Documents/GitHub/ChemEProjects/Ethanol-Water-Material-Balance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3af6bdb6fd02cc28/Documents/GitHub/ChemEProjects/Ethanol_Water_Steady_State_Separation_Recycle_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="883" documentId="8_{66A1A9FC-005E-44AA-8839-2039AE58A330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B20BA9B-6A83-4826-AF0D-B7A081EC7343}"/>
+  <xr:revisionPtr revIDLastSave="885" documentId="8_{66A1A9FC-005E-44AA-8839-2039AE58A330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DB59D03-1B1B-4193-964C-9E9D151DC0F8}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="1" xr2:uid="{F31F3049-9973-4664-9FE7-54287E385AA7}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Steady-State Recycle Model" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterate="1" iterateCount="1000" iterateDelta="9.9999999999999995E-7" calcCompleted="0"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -485,9 +484,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="185" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -652,7 +651,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -688,10 +687,10 @@
     <xf numFmtId="10" fontId="0" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -699,11 +698,10 @@
     <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="185" fontId="0" fillId="15" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="15" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -5274,7 +5272,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> balances closed to approximately 0 kg/hr. This validates conservation of mass in the steady-state model.</a:t>
+            <a:t> balances are approximately 0 kg/hr. This validates conservation of mass in the steady-state model.</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
@@ -5283,10 +5281,6 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7068,7 +7062,7 @@
       <c r="A47" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B47" s="46">
+      <c r="B47" s="11">
         <f ca="1">C23-C28-C34</f>
         <v>0</v>
       </c>
@@ -7080,7 +7074,7 @@
       <c r="A48" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="46">
+      <c r="B48" s="11">
         <f ca="1">C5-C28-C44</f>
         <v>0</v>
       </c>
